--- a/mock/raw/CP01.xlsx
+++ b/mock/raw/CP01.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -955,7 +955,7 @@
       <c r="J12" s="4" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="6" t="n"/>
+      <c r="A13" s="7" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="4" t="inlineStr">
@@ -991,7 +991,11 @@
       <c r="J13" s="4" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="6" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스태킹</t>
+        </is>
+      </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="4" t="inlineStr">
@@ -999,35 +1003,39 @@
           <t>both</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>전극 언와인더</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>노칭 프레스</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>원단 장력</t>
+          <t>노칭 피치</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>25±3N</t>
+          <t>50±0.2mm</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>장력계</t>
+          <t>레이저 변위계</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>장력 조건 재설정</t>
+          <t>피치 보정 후 초도품 확인</t>
         </is>
       </c>
       <c r="J14" s="4" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="6" t="n"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>조립</t>
+        </is>
+      </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="4" t="inlineStr">
@@ -1035,35 +1043,34 @@
           <t>both</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>〃</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>전극 언와인더</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>사행량</t>
+          <t>원단 장력</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>±1.0mm</t>
+          <t>25±3N</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>EPC 센서</t>
+          <t>장력계</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>가이드 롤 재조정</t>
+          <t>장력 조건 재설정</t>
         </is>
       </c>
       <c r="J15" s="4" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="4" t="inlineStr">
@@ -1071,648 +1078,669 @@
           <t>both</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>사행량</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>±1.0mm</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>EPC 센서</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>가이드 롤 재조정</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>노칭 프레스</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>타발 속도</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>120±10spm</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>속도 조건 재설정</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>금형 클리어런스</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>22±2㎛</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>간극 게이지</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>클리어런스 재조정</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>OP-20</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>스태킹</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>분리막 언와인더</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>분리막 장력</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>8±1N</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>장력계</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>장력 조건 재설정</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="J19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>스태커</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>흡착 압력</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>-60±5kPa</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>진공계</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>흡착 패드 교체</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>적층 속도</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>60±5ppm</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>속도 조건 재설정</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>OP-30</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>cathode 탭용접</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>cathode</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>초음파 융착기</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>용접 진폭</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>40±3㎛</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>진폭계</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>혼 교체 후 초도품 확인</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>cathode</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>용접 출력</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>2.0±0.2kW</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>출력 조건 재설정</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>OP-31</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>anode 탭용접</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>anode</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>초음파 융착기</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>용접 진폭</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>35±3㎛</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>진폭계</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>혼 교체 후 초도품 확인</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="J24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>anode</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>용접 출력</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>1.8±0.2kW</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>출력 조건 재설정</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>OP-40</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>패키징</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>파우치 포밍기</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>포밍 깊이</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>8±0.3mm</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>깊이 게이지</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>포밍 금형 점검</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>포밍 외관</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>균열 없을 것</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>육안 검사</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>금형 교체</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>OP-50</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>전해액주입</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>주액기</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>주액량</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>2.4±0.05g</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>중량 검사기</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>노즐 세척 후 재주액</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>챔버 진공도</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>5±1Pa</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>진공계</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>진공 펌프 점검</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>OP-60</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>실링</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>실러</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>실링 압력</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>0.4±0.05MPa</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>압력계</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>실링 패드 교체</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>실링 시간</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>3.0±0.2s</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>실링 조건 재설정</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>실링 폭</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>5±0.5mm</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>게이지</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>실링 조건 재설정</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B27:B28"/>
+  <mergeCells count="22">
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C11:C17"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B11:B18"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C18:C20"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A15:A32"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A4:A31"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C11:C18"/>
+    <mergeCell ref="A4:A13"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B26:B27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mock/raw/CP01.xlsx
+++ b/mock/raw/CP01.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>실링</t>
+          <t>사이드 실링</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>실링</t>
+          <t>사이드 실링</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1649,7 +1649,11 @@
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>프리 실링</t>
+        </is>
+      </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -1684,7 +1688,11 @@
     </row>
     <row r="32">
       <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>사이드 실링</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -1718,19 +1726,18 @@
       <c r="J32" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="21">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C24:C25"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="B11:B18"/>
     <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C30:C32"/>
     <mergeCell ref="A15:A32"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B22:B23"/>
@@ -1739,7 +1746,7 @@
     <mergeCell ref="C11:C18"/>
     <mergeCell ref="A4:A13"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B19:B21"/>
     <mergeCell ref="B26:B27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mock/raw/CP01.xlsx
+++ b/mock/raw/CP01.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -996,8 +996,8 @@
           <t>스태킹</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -1036,718 +1036,769 @@
           <t>조립</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OP-30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cathode 탭용접</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>anode</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>초음파 융착기</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>용접 강도</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8N 이상</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>인장시험기</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>용접 조건 재설정 후 초도품 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>조립</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OP-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>노칭</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>전극 언와인더</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>원단 장력</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>25±3N</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>장력계</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>장력 조건 재설정</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>사행량</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>±1.0mm</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>EPC 센서</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>가이드 롤 재조정</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="J17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>노칭 프레스</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>타발 속도</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>120±10spm</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>속도 조건 재설정</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>금형 클리어런스</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>22±2㎛</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>간극 게이지</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>클리어런스 재조정</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>OP-20</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>스태킹</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>분리막 언와인더</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>분리막 장력</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>8±1N</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>장력계</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>장력 조건 재설정</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="J20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>스태커</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>흡착 압력</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>-60±5kPa</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>진공계</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>흡착 패드 교체</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>적층 속도</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>60±5ppm</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>속도 조건 재설정</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>OP-30</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>cathode 탭용접</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>cathode</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>초음파 융착기</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>용접 진폭</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>40±3㎛</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>진폭계</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>혼 교체 후 초도품 확인</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>cathode</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>용접 출력</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>2.0±0.2kW</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>출력 조건 재설정</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="J24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>OP-31</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>anode 탭용접</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>anode</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>초음파 융착기</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>용접 진폭</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>35±3㎛</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>진폭계</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>혼 교체 후 초도품 확인</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>anode</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>용접 출력</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>1.8±0.2kW</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>출력 조건 재설정</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>OP-40</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>패키징</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>파우치 포밍기</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>포밍 깊이</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>8±0.3mm</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>깊이 게이지</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>포밍 금형 점검</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>포밍 외관</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>균열 없을 것</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>육안 검사</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>금형 교체</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>OP-50</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>전해액주입</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>주액기</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>주액량</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>2.4±0.05g</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>중량 검사기</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>노즐 세척 후 재주액</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>챔버 진공도</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>5±1Pa</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>진공계</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>진공 펌프 점검</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>OP-60</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>사이드 실링</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>실러</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>실링 압력</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>0.4±0.05MPa</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>압력계</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>실링 패드 교체</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" t="inlineStr">
+      <c r="J31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" t="inlineStr">
         <is>
           <t>프리 실링</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>실링 시간</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>3.0±0.2s</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>설비 로그</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>실링 조건 재설정</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" t="inlineStr">
+      <c r="J32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" t="inlineStr">
         <is>
           <t>사이드 실링</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>실링 폭</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>5±0.5mm</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>게이지</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>실링 조건 재설정</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
+    <mergeCell ref="B27:B28"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="B11:B18"/>
-    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C16:C19"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B31:B33"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A15:A32"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C11:C14"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B22:B23"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C11:C18"/>
     <mergeCell ref="A4:A13"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A16:A33"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B16:B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
